--- a/SGC-CKN/Excel/99a257cb-7f2e-419d-aa86-c33c921201a2_Lô_CT-02_P1-181_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/99a257cb-7f2e-419d-aa86-c33c921201a2_Lô_CT-02_P1-181_D800_23-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -173,6 +173,10 @@
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:48
+23/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">12:15
@@ -325,17 +329,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -361,6 +360,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -496,53 +500,53 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1148,16 +1152,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-0.7</v>
+        <v>-3.7</v>
       </c>
       <c r="H11" s="5">
         <v>0.33</v>
       </c>
       <c r="I11" s="5">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J11" s="8">
-        <v>2.1</v>
+        <v>11.1</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1180,10 +1184,10 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-0.7</v>
+        <v>-3.7</v>
       </c>
       <c r="G12" s="9">
-        <v>-3.7</v>
+        <v>-6.7</v>
       </c>
       <c r="H12" s="9">
         <v>0.33</v>
@@ -1191,7 +1195,7 @@
       <c r="I12" s="9">
         <v>3</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="8">
         <v>9</v>
       </c>
       <c r="K12" s="10" t="s">
@@ -1199,177 +1203,177 @@
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="13">
-        <v>-3.7</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="F13" s="12">
         <v>-6.7</v>
       </c>
-      <c r="H13" s="13">
+      <c r="G13" s="12">
+        <v>-16.2</v>
+      </c>
+      <c r="H13" s="12">
         <v>0.5</v>
       </c>
-      <c r="I13" s="13">
-        <v>3</v>
-      </c>
-      <c r="J13" s="12">
-        <v>6</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="I13" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="J13" s="8">
+        <v>19</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="16">
-        <v>-6.7</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="15">
         <v>-16.2</v>
       </c>
-      <c r="H14" s="16">
+      <c r="G14" s="15">
+        <v>-21.2</v>
+      </c>
+      <c r="H14" s="15">
         <v>0.67</v>
       </c>
-      <c r="I14" s="16">
-        <v>9.5</v>
-      </c>
-      <c r="J14" s="12">
-        <v>14.25</v>
-      </c>
-      <c r="K14" s="17" t="s">
+      <c r="I14" s="15">
+        <v>5</v>
+      </c>
+      <c r="J14" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19">
-        <v>-16.2</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-24.2</v>
-      </c>
-      <c r="H15" s="19">
+      <c r="F15" s="18">
+        <v>-21.2</v>
+      </c>
+      <c r="G15" s="18">
+        <v>-25.7</v>
+      </c>
+      <c r="H15" s="18">
         <v>0.33</v>
       </c>
-      <c r="I15" s="19">
-        <v>8</v>
-      </c>
-      <c r="J15" s="12">
-        <v>24</v>
-      </c>
-      <c r="K15" s="20" t="s">
+      <c r="I15" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="8">
+        <v>13.5</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="22">
-        <v>-24.2</v>
-      </c>
-      <c r="G16" s="22">
+      <c r="F16" s="21">
         <v>-25.7</v>
       </c>
-      <c r="H16" s="22">
+      <c r="G16" s="21">
+        <v>-35.7</v>
+      </c>
+      <c r="H16" s="21">
         <v>0.58</v>
       </c>
-      <c r="I16" s="22">
-        <v>1.5</v>
+      <c r="I16" s="21">
+        <v>10</v>
       </c>
       <c r="J16" s="8">
-        <v>2.57</v>
-      </c>
-      <c r="K16" s="23" t="s">
+        <v>17.14</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="25">
-        <v>-25.7</v>
-      </c>
-      <c r="G17" s="25">
+      <c r="F17" s="24">
+        <v>-35.7</v>
+      </c>
+      <c r="G17" s="24">
         <v>-39.9</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>1.03</v>
       </c>
-      <c r="I17" s="25">
-        <v>14.2</v>
-      </c>
-      <c r="J17" s="12">
-        <v>13.74</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="I17" s="24">
+        <v>4.2</v>
+      </c>
+      <c r="J17" s="27">
+        <v>4.06</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1384,10 +1388,10 @@
         <v>50</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-39.9</v>
@@ -1396,13 +1400,13 @@
         <v>-44.33</v>
       </c>
       <c r="H18" s="28">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="I18" s="28">
         <v>4.43</v>
       </c>
-      <c r="J18" s="12">
-        <v>9.49</v>
+      <c r="J18" s="8">
+        <v>9.84</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1410,7 +1414,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1516,31 +1520,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1560,16 +1564,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-0.7</v>
+        <v>-3.7</v>
       </c>
       <c r="G2" s="5">
         <v>0.33</v>
       </c>
       <c r="H2" s="5">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="I2" s="8">
-        <v>2.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1586,10 +1590,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-0.7</v>
+        <v>-3.7</v>
       </c>
       <c r="F3" s="9">
-        <v>-3.7</v>
+        <v>-6.7</v>
       </c>
       <c r="G3" s="9">
         <v>0.33</v>
@@ -1597,153 +1601,153 @@
       <c r="H3" s="9">
         <v>3</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-3.7</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
         <v>-6.7</v>
       </c>
-      <c r="G4" s="13">
+      <c r="F4" s="12">
+        <v>-16.2</v>
+      </c>
+      <c r="G4" s="12">
         <v>0.5</v>
       </c>
-      <c r="H4" s="13">
-        <v>3</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="H4" s="12">
+        <v>9.5</v>
+      </c>
+      <c r="I4" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
+        <v>-16.2</v>
+      </c>
+      <c r="F5" s="15">
+        <v>-21.2</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.67</v>
+      </c>
+      <c r="H5" s="15">
+        <v>5</v>
+      </c>
+      <c r="I5" s="8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1</v>
+      </c>
+      <c r="E6" s="18">
+        <v>-21.2</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-25.7</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.33</v>
+      </c>
+      <c r="H6" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="I6" s="8">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C7" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-6.7</v>
-      </c>
-      <c r="F5" s="16">
-        <v>-16.2</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.67</v>
-      </c>
-      <c r="H5" s="16">
-        <v>9.5</v>
-      </c>
-      <c r="I5" s="12">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="E7" s="21">
+        <v>-25.7</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-35.7</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0.58</v>
+      </c>
+      <c r="H7" s="21">
+        <v>10</v>
+      </c>
+      <c r="I7" s="8">
+        <v>17.14</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-16.2</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-24.2</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.33</v>
-      </c>
-      <c r="H6" s="19">
-        <v>8</v>
-      </c>
-      <c r="I6" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
-        <v>6</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="22">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
-        <v>-24.2</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-25.7</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.58</v>
-      </c>
-      <c r="H7" s="22">
-        <v>1.5</v>
-      </c>
-      <c r="I7" s="8">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>7</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="25">
-        <v>1</v>
-      </c>
-      <c r="E8" s="25">
-        <v>-25.7</v>
-      </c>
-      <c r="F8" s="25">
+      <c r="E8" s="24">
+        <v>-35.7</v>
+      </c>
+      <c r="F8" s="24">
         <v>-39.9</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>1.03</v>
       </c>
-      <c r="H8" s="25">
-        <v>14.2</v>
-      </c>
-      <c r="I8" s="12">
-        <v>13.74</v>
+      <c r="H8" s="24">
+        <v>4.2</v>
+      </c>
+      <c r="I8" s="27">
+        <v>4.06</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1766,18 +1770,18 @@
         <v>-44.33</v>
       </c>
       <c r="G9" s="28">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H9" s="28">
         <v>4.43</v>
       </c>
-      <c r="I9" s="12">
-        <v>9.49</v>
+      <c r="I9" s="8">
+        <v>9.84</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
@@ -1795,13 +1799,13 @@
         <v>-44.33</v>
       </c>
       <c r="G10" s="33">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="H10" s="33">
         <v>44.33</v>
       </c>
       <c r="I10" s="33">
-        <v>10.43</v>
+        <v>10.47</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/99a257cb-7f2e-419d-aa86-c33c921201a2_Lô_CT-02_P1-181_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/99a257cb-7f2e-419d-aa86-c33c921201a2_Lô_CT-02_P1-181_D800_23-03-2026.xlsx
@@ -92,7 +92,7 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>1</t>
+    <t>1.Đất thổ nhưỡng</t>
   </si>
   <si>
     <t>Đất thổ nhưỡng</t>
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">08:40
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">09:10
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:10
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">10:45
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:47
@@ -172,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">11:48
